--- a/Excel/EquipSetConfig.xlsx
+++ b/Excel/EquipSetConfig.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="普通装备" sheetId="1" r:id="rId1"/>
+    <sheet name="特殊装备" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -1060,7 +1061,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:J50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="6" width="16.25" style="1" customWidth="1"/>
@@ -1070,12 +1071,12 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10">
+    <row r="1" customHeight="1" spans="3:10">
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="13.5" spans="3:10">
+    <row r="3" customHeight="1" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1098,7 +1099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:10">
+    <row r="4" customHeight="1" spans="3:10">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1121,7 +1122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:10">
+    <row r="5" customHeight="1" spans="3:10">
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1144,7 +1145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="3:10">
+    <row r="6" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1170,7 +1171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="3:10">
+    <row r="7" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1196,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="3:10">
+    <row r="8" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1222,7 +1223,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="3:10">
+    <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1248,7 +1249,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="3:10">
+    <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1274,7 +1275,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="3:10">
+    <row r="11" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1300,7 +1301,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="3:10">
+    <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1326,7 +1327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="3:10">
+    <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1352,7 +1353,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="3:10">
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1378,7 +1379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="3:10">
+    <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
         <v>10</v>
       </c>
@@ -1404,7 +1405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="3:10">
+    <row r="17" customHeight="1" spans="3:10">
       <c r="C17" s="1">
         <v>11</v>
       </c>
@@ -1430,7 +1431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="3:10">
+    <row r="18" customHeight="1" spans="3:10">
       <c r="C18" s="1">
         <v>12</v>
       </c>
@@ -1456,7 +1457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="3:10">
+    <row r="19" customHeight="1" spans="3:10">
       <c r="C19" s="1">
         <v>13</v>
       </c>
@@ -1482,7 +1483,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="3:10">
+    <row r="20" customHeight="1" spans="3:10">
       <c r="C20" s="1">
         <v>14</v>
       </c>
@@ -1508,7 +1509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="3:10">
+    <row r="21" customHeight="1" spans="3:10">
       <c r="C21" s="1">
         <v>15</v>
       </c>
@@ -1534,7 +1535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="3:10">
+    <row r="22" customHeight="1" spans="3:10">
       <c r="C22" s="1">
         <v>16</v>
       </c>
@@ -1560,7 +1561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="3:10">
+    <row r="23" customHeight="1" spans="3:10">
       <c r="C23" s="1">
         <v>17</v>
       </c>
@@ -1586,7 +1587,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="3:10">
+    <row r="24" customHeight="1" spans="3:10">
       <c r="C24" s="1">
         <v>18</v>
       </c>
@@ -1612,7 +1613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="3:10">
+    <row r="26" customHeight="1" spans="3:10">
       <c r="C26" s="1">
         <v>19</v>
       </c>
@@ -1638,7 +1639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="3:10">
+    <row r="27" customHeight="1" spans="3:10">
       <c r="C27" s="1">
         <v>20</v>
       </c>
@@ -1664,7 +1665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="3:10">
+    <row r="28" customHeight="1" spans="3:10">
       <c r="C28" s="1">
         <v>21</v>
       </c>
@@ -1690,7 +1691,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="3:10">
+    <row r="29" customHeight="1" spans="3:10">
       <c r="C29" s="1">
         <v>22</v>
       </c>
@@ -1716,7 +1717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="3:10">
+    <row r="30" customHeight="1" spans="3:10">
       <c r="C30" s="1">
         <v>23</v>
       </c>
@@ -1742,7 +1743,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="3:10">
+    <row r="31" customHeight="1" spans="3:10">
       <c r="C31" s="1">
         <v>24</v>
       </c>
@@ -1768,7 +1769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="3:10">
+    <row r="32" customHeight="1" spans="3:10">
       <c r="C32" s="1">
         <v>25</v>
       </c>
@@ -1794,7 +1795,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="3:10">
+    <row r="33" customHeight="1" spans="3:10">
       <c r="C33" s="1">
         <v>26</v>
       </c>
@@ -1820,7 +1821,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="3:10">
+    <row r="34" customHeight="1" spans="3:10">
       <c r="C34" s="1">
         <v>27</v>
       </c>
@@ -1846,7 +1847,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="3:10">
+    <row r="35" customHeight="1" spans="3:10">
       <c r="C35" s="1">
         <v>28</v>
       </c>
@@ -1872,7 +1873,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="3:10">
+    <row r="36" customHeight="1" spans="3:10">
       <c r="C36" s="1">
         <v>29</v>
       </c>
@@ -1898,7 +1899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="3:10">
+    <row r="37" customHeight="1" spans="3:10">
       <c r="C37" s="1">
         <v>30</v>
       </c>
@@ -1924,7 +1925,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="3:10">
+    <row r="39" customHeight="1" spans="3:10">
       <c r="C39" s="1">
         <v>31</v>
       </c>
@@ -1950,7 +1951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="3:10">
+    <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
         <v>32</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="3:10">
+    <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
         <v>33</v>
       </c>
@@ -2002,7 +2003,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="3:10">
+    <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
         <v>34</v>
       </c>
@@ -2028,7 +2029,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="3:10">
+    <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
         <v>35</v>
       </c>
@@ -2054,7 +2055,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="3:10">
+    <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
         <v>36</v>
       </c>
@@ -2080,7 +2081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="3:10">
+    <row r="45" customHeight="1" spans="3:10">
       <c r="C45" s="1">
         <v>37</v>
       </c>
@@ -2106,7 +2107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="3:10">
+    <row r="46" customHeight="1" spans="3:10">
       <c r="C46" s="1">
         <v>38</v>
       </c>
@@ -2132,7 +2133,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="3:10">
+    <row r="47" customHeight="1" spans="3:10">
       <c r="C47" s="1">
         <v>39</v>
       </c>
@@ -2158,7 +2159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="3:10">
+    <row r="48" customHeight="1" spans="3:10">
       <c r="C48" s="1">
         <v>40</v>
       </c>
@@ -2184,7 +2185,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="3:10">
+    <row r="49" customHeight="1" spans="3:10">
       <c r="C49" s="1">
         <v>41</v>
       </c>
@@ -2210,7 +2211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="3:10">
+    <row r="50" customHeight="1" spans="3:10">
       <c r="C50" s="1">
         <v>42</v>
       </c>
@@ -2245,4 +2246,207 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="6" width="16.25" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>101</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>81</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>101</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>82</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>101</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1">
+        <v>83</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>101</v>
+      </c>
+      <c r="F9" s="1">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1">
+        <v>84</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Excel/EquipSetConfig.xlsx
+++ b/Excel/EquipSetConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="15">
   <si>
     <t>#</t>
   </si>
@@ -63,46 +63,16 @@
     <t>double</t>
   </si>
   <si>
-    <t>生命增幅</t>
+    <t>金币加成</t>
   </si>
   <si>
-    <t>防御增幅</t>
+    <t>经验加成</t>
   </si>
   <si>
-    <t>物攻增幅</t>
+    <t>品质加成</t>
   </si>
   <si>
-    <t>魔法增幅</t>
-  </si>
-  <si>
-    <t>道攻增幅</t>
-  </si>
-  <si>
-    <t>物攻倍率</t>
-  </si>
-  <si>
-    <t>物伤倍率</t>
-  </si>
-  <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
-    <t>魔法倍率</t>
-  </si>
-  <si>
-    <t>法伤倍率</t>
-  </si>
-  <si>
-    <t>道攻倍率</t>
-  </si>
-  <si>
-    <t>道伤倍率</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
-    <t>韧性倍率</t>
+    <t>爆率加成</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1030,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:J50"/>
+  <dimension ref="C1:J17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1159,16 +1129,13 @@
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>2002</v>
+        <v>1004</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:10">
@@ -1185,16 +1152,13 @@
         <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>2001</v>
+        <v>1003</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:10">
@@ -1208,19 +1172,16 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>2004</v>
+        <v>1002</v>
       </c>
       <c r="H8" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" s="1">
-        <v>2</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:10">
@@ -1228,25 +1189,22 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>2002</v>
+        <v>1001</v>
       </c>
       <c r="H9" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:10">
@@ -1260,19 +1218,16 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>2001</v>
+        <v>1005</v>
       </c>
       <c r="H10" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:10">
@@ -1286,19 +1241,16 @@
         <v>1</v>
       </c>
       <c r="F11" s="1">
+        <v>6</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1003</v>
+      </c>
+      <c r="H11" s="1">
         <v>10</v>
       </c>
-      <c r="G11" s="1">
-        <v>2005</v>
-      </c>
-      <c r="H11" s="1">
-        <v>2</v>
-      </c>
       <c r="I11" s="1">
-        <v>2</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:10">
@@ -1306,25 +1258,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>2002</v>
+        <v>1002</v>
       </c>
       <c r="H12" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:10">
@@ -1332,25 +1281,22 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>2001</v>
+        <v>1001</v>
       </c>
       <c r="H13" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:10">
@@ -1364,877 +1310,85 @@
         <v>1</v>
       </c>
       <c r="F14" s="1">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1006</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:10">
+      <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="G14" s="1">
-        <v>2006</v>
-      </c>
-      <c r="H14" s="1">
-        <v>2</v>
-      </c>
-      <c r="I14" s="1">
-        <v>2</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>15</v>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1003</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1002</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5</v>
+      </c>
+      <c r="I16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:9">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
         <v>10</v>
       </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2004</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="1">
-        <v>20</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
-      <c r="C17" s="1">
-        <v>11</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1">
-        <v>6</v>
-      </c>
       <c r="G17" s="1">
-        <v>2007</v>
+        <v>1001</v>
       </c>
       <c r="H17" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I17" s="1">
-        <v>30</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:10">
-      <c r="C18" s="1">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="F18" s="1">
-        <v>10</v>
-      </c>
-      <c r="G18" s="1">
-        <v>2003</v>
-      </c>
-      <c r="H18" s="1">
-        <v>40</v>
-      </c>
-      <c r="I18" s="1">
-        <v>40</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
-      <c r="C19" s="1">
-        <v>13</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1">
-        <v>2</v>
-      </c>
-      <c r="G19" s="1">
-        <v>2005</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="1">
-        <v>20</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
-      <c r="C20" s="1">
-        <v>14</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2</v>
-      </c>
-      <c r="F20" s="1">
-        <v>6</v>
-      </c>
-      <c r="G20" s="1">
-        <v>2008</v>
-      </c>
-      <c r="H20" s="1">
-        <v>30</v>
-      </c>
-      <c r="I20" s="1">
-        <v>30</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:10">
-      <c r="C21" s="1">
-        <v>15</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>2</v>
-      </c>
-      <c r="F21" s="1">
-        <v>10</v>
-      </c>
-      <c r="G21" s="1">
-        <v>2003</v>
-      </c>
-      <c r="H21" s="1">
-        <v>40</v>
-      </c>
-      <c r="I21" s="1">
-        <v>40</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:10">
-      <c r="C22" s="1">
-        <v>16</v>
-      </c>
-      <c r="D22" s="1">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1">
-        <v>2</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1">
-        <v>2006</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="1">
-        <v>20</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:10">
-      <c r="C23" s="1">
-        <v>17</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1">
-        <v>2</v>
-      </c>
-      <c r="F23" s="1">
-        <v>6</v>
-      </c>
-      <c r="G23" s="1">
-        <v>2009</v>
-      </c>
-      <c r="H23" s="1">
-        <v>30</v>
-      </c>
-      <c r="I23" s="1">
-        <v>30</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:10">
-      <c r="C24" s="1">
-        <v>18</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2</v>
-      </c>
-      <c r="F24" s="1">
-        <v>10</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2003</v>
-      </c>
-      <c r="H24" s="1">
-        <v>40</v>
-      </c>
-      <c r="I24" s="1">
-        <v>40</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:10">
-      <c r="C26" s="1">
-        <v>19</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
-        <v>3</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2</v>
-      </c>
-      <c r="G26" s="1">
-        <v>2004</v>
-      </c>
-      <c r="H26" s="1">
-        <v>40</v>
-      </c>
-      <c r="I26" s="1">
-        <v>40</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:10">
-      <c r="C27" s="1">
-        <v>20</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1">
-        <v>3</v>
-      </c>
-      <c r="F27" s="1">
-        <v>6</v>
-      </c>
-      <c r="G27" s="1">
-        <v>2007</v>
-      </c>
-      <c r="H27" s="1">
-        <v>60</v>
-      </c>
-      <c r="I27" s="1">
-        <v>60</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:10">
-      <c r="C28" s="1">
-        <v>21</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1">
-        <v>3</v>
-      </c>
-      <c r="F28" s="1">
-        <v>8</v>
-      </c>
-      <c r="G28" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H28" s="1">
-        <v>80</v>
-      </c>
-      <c r="I28" s="1">
-        <v>80</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:10">
-      <c r="C29" s="1">
-        <v>22</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1">
-        <v>3</v>
-      </c>
-      <c r="F29" s="1">
-        <v>10</v>
-      </c>
-      <c r="G29" s="1">
-        <v>2012</v>
-      </c>
-      <c r="H29" s="1">
-        <v>40</v>
-      </c>
-      <c r="I29" s="1">
-        <v>40</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:10">
-      <c r="C30" s="1">
-        <v>23</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2</v>
-      </c>
-      <c r="E30" s="1">
-        <v>3</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2</v>
-      </c>
-      <c r="G30" s="1">
-        <v>2005</v>
-      </c>
-      <c r="H30" s="1">
-        <v>40</v>
-      </c>
-      <c r="I30" s="1">
-        <v>40</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:10">
-      <c r="C31" s="1">
-        <v>24</v>
-      </c>
-      <c r="D31" s="1">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1">
-        <v>3</v>
-      </c>
-      <c r="F31" s="1">
-        <v>6</v>
-      </c>
-      <c r="G31" s="1">
-        <v>2008</v>
-      </c>
-      <c r="H31" s="1">
-        <v>60</v>
-      </c>
-      <c r="I31" s="1">
-        <v>60</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:10">
-      <c r="C32" s="1">
-        <v>25</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2</v>
-      </c>
-      <c r="E32" s="1">
-        <v>3</v>
-      </c>
-      <c r="F32" s="1">
-        <v>8</v>
-      </c>
-      <c r="G32" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H32" s="1">
-        <v>80</v>
-      </c>
-      <c r="I32" s="1">
-        <v>80</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:10">
-      <c r="C33" s="1">
-        <v>26</v>
-      </c>
-      <c r="D33" s="1">
-        <v>2</v>
-      </c>
-      <c r="E33" s="1">
-        <v>3</v>
-      </c>
-      <c r="F33" s="1">
-        <v>10</v>
-      </c>
-      <c r="G33" s="1">
-        <v>2012</v>
-      </c>
-      <c r="H33" s="1">
-        <v>40</v>
-      </c>
-      <c r="I33" s="1">
-        <v>40</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:10">
-      <c r="C34" s="1">
-        <v>27</v>
-      </c>
-      <c r="D34" s="1">
-        <v>3</v>
-      </c>
-      <c r="E34" s="1">
-        <v>3</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2</v>
-      </c>
-      <c r="G34" s="1">
-        <v>2006</v>
-      </c>
-      <c r="H34" s="1">
-        <v>40</v>
-      </c>
-      <c r="I34" s="1">
-        <v>40</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:10">
-      <c r="C35" s="1">
-        <v>28</v>
-      </c>
-      <c r="D35" s="1">
-        <v>3</v>
-      </c>
-      <c r="E35" s="1">
-        <v>3</v>
-      </c>
-      <c r="F35" s="1">
-        <v>6</v>
-      </c>
-      <c r="G35" s="1">
-        <v>2009</v>
-      </c>
-      <c r="H35" s="1">
-        <v>60</v>
-      </c>
-      <c r="I35" s="1">
-        <v>60</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:10">
-      <c r="C36" s="1">
-        <v>29</v>
-      </c>
-      <c r="D36" s="1">
-        <v>3</v>
-      </c>
-      <c r="E36" s="1">
-        <v>3</v>
-      </c>
-      <c r="F36" s="1">
-        <v>8</v>
-      </c>
-      <c r="G36" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H36" s="1">
-        <v>80</v>
-      </c>
-      <c r="I36" s="1">
-        <v>80</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:10">
-      <c r="C37" s="1">
-        <v>30</v>
-      </c>
-      <c r="D37" s="1">
-        <v>3</v>
-      </c>
-      <c r="E37" s="1">
-        <v>3</v>
-      </c>
-      <c r="F37" s="1">
-        <v>10</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2012</v>
-      </c>
-      <c r="H37" s="1">
-        <v>40</v>
-      </c>
-      <c r="I37" s="1">
-        <v>40</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:10">
-      <c r="C39" s="1">
-        <v>31</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
-        <v>4</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2</v>
-      </c>
-      <c r="G39" s="1">
-        <v>2004</v>
-      </c>
-      <c r="H39" s="1">
-        <v>60</v>
-      </c>
-      <c r="I39" s="1">
-        <v>60</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:10">
-      <c r="C40" s="1">
-        <v>32</v>
-      </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
-        <v>4</v>
-      </c>
-      <c r="F40" s="1">
-        <v>6</v>
-      </c>
-      <c r="G40" s="1">
-        <v>2007</v>
-      </c>
-      <c r="H40" s="1">
-        <v>90</v>
-      </c>
-      <c r="I40" s="1">
-        <v>90</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:10">
-      <c r="C41" s="1">
-        <v>33</v>
-      </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
-        <v>4</v>
-      </c>
-      <c r="F41" s="1">
-        <v>8</v>
-      </c>
-      <c r="G41" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H41" s="1">
-        <v>120</v>
-      </c>
-      <c r="I41" s="1">
-        <v>120</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:10">
-      <c r="C42" s="1">
-        <v>34</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
-        <v>4</v>
-      </c>
-      <c r="F42" s="1">
-        <v>10</v>
-      </c>
-      <c r="G42" s="1">
-        <v>2012</v>
-      </c>
-      <c r="H42" s="1">
-        <v>60</v>
-      </c>
-      <c r="I42" s="1">
-        <v>60</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:10">
-      <c r="C43" s="1">
-        <v>35</v>
-      </c>
-      <c r="D43" s="1">
-        <v>2</v>
-      </c>
-      <c r="E43" s="1">
-        <v>4</v>
-      </c>
-      <c r="F43" s="1">
-        <v>2</v>
-      </c>
-      <c r="G43" s="1">
-        <v>2005</v>
-      </c>
-      <c r="H43" s="1">
-        <v>60</v>
-      </c>
-      <c r="I43" s="1">
-        <v>60</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:10">
-      <c r="C44" s="1">
-        <v>36</v>
-      </c>
-      <c r="D44" s="1">
-        <v>2</v>
-      </c>
-      <c r="E44" s="1">
-        <v>4</v>
-      </c>
-      <c r="F44" s="1">
-        <v>6</v>
-      </c>
-      <c r="G44" s="1">
-        <v>2008</v>
-      </c>
-      <c r="H44" s="1">
-        <v>90</v>
-      </c>
-      <c r="I44" s="1">
-        <v>90</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:10">
-      <c r="C45" s="1">
-        <v>37</v>
-      </c>
-      <c r="D45" s="1">
-        <v>2</v>
-      </c>
-      <c r="E45" s="1">
-        <v>4</v>
-      </c>
-      <c r="F45" s="1">
-        <v>8</v>
-      </c>
-      <c r="G45" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H45" s="1">
-        <v>120</v>
-      </c>
-      <c r="I45" s="1">
-        <v>120</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:10">
-      <c r="C46" s="1">
-        <v>38</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="1">
-        <v>4</v>
-      </c>
-      <c r="F46" s="1">
-        <v>10</v>
-      </c>
-      <c r="G46" s="1">
-        <v>2012</v>
-      </c>
-      <c r="H46" s="1">
-        <v>60</v>
-      </c>
-      <c r="I46" s="1">
-        <v>60</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:10">
-      <c r="C47" s="1">
-        <v>39</v>
-      </c>
-      <c r="D47" s="1">
-        <v>3</v>
-      </c>
-      <c r="E47" s="1">
-        <v>4</v>
-      </c>
-      <c r="F47" s="1">
-        <v>2</v>
-      </c>
-      <c r="G47" s="1">
-        <v>2006</v>
-      </c>
-      <c r="H47" s="1">
-        <v>60</v>
-      </c>
-      <c r="I47" s="1">
-        <v>60</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:10">
-      <c r="C48" s="1">
-        <v>40</v>
-      </c>
-      <c r="D48" s="1">
-        <v>3</v>
-      </c>
-      <c r="E48" s="1">
-        <v>4</v>
-      </c>
-      <c r="F48" s="1">
-        <v>6</v>
-      </c>
-      <c r="G48" s="1">
-        <v>2009</v>
-      </c>
-      <c r="H48" s="1">
-        <v>90</v>
-      </c>
-      <c r="I48" s="1">
-        <v>90</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:10">
-      <c r="C49" s="1">
-        <v>41</v>
-      </c>
-      <c r="D49" s="1">
-        <v>3</v>
-      </c>
-      <c r="E49" s="1">
-        <v>4</v>
-      </c>
-      <c r="F49" s="1">
-        <v>8</v>
-      </c>
-      <c r="G49" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H49" s="1">
-        <v>120</v>
-      </c>
-      <c r="I49" s="1">
-        <v>120</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:10">
-      <c r="C50" s="1">
-        <v>42</v>
-      </c>
-      <c r="D50" s="1">
-        <v>3</v>
-      </c>
-      <c r="E50" s="1">
-        <v>4</v>
-      </c>
-      <c r="F50" s="1">
-        <v>10</v>
-      </c>
-      <c r="G50" s="1">
-        <v>2012</v>
-      </c>
-      <c r="H50" s="1">
-        <v>60</v>
-      </c>
-      <c r="I50" s="1">
-        <v>60</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2437,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipSetConfig.xlsx
+++ b/Excel/EquipSetConfig.xlsx
@@ -1152,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="H7" s="1">
         <v>10</v>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="H9" s="1">
         <v>5</v>
@@ -1244,7 +1244,7 @@
         <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -1290,7 +1290,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="H13" s="1">
         <v>5</v>
@@ -1336,7 +1336,7 @@
         <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="H15" s="1">
         <v>10</v>
@@ -1382,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="H17" s="1">
         <v>5</v>

--- a/Excel/EquipSetConfig.xlsx
+++ b/Excel/EquipSetConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="14">
   <si>
     <t>#</t>
   </si>
@@ -45,22 +45,19 @@
     <t>Count</t>
   </si>
   <si>
-    <t>AttrId</t>
+    <t>AtrId</t>
   </si>
   <si>
-    <t>AttrValue</t>
+    <t>AtrValue</t>
   </si>
   <si>
-    <t>AttrRise</t>
+    <t>RiseType</t>
   </si>
   <si>
     <t>Id</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>double</t>
   </si>
   <si>
     <t>金币加成</t>
@@ -1112,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="3:10">
@@ -1135,7 +1132,7 @@
         <v>5</v>
       </c>
       <c r="I6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:10">
@@ -1158,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:10">
@@ -1181,7 +1178,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:10">
@@ -1204,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:10">
@@ -1227,7 +1224,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:10">
@@ -1250,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:10">
@@ -1273,7 +1270,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:10">
@@ -1296,7 +1293,7 @@
         <v>5</v>
       </c>
       <c r="I13" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:10">
@@ -1319,7 +1316,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:10">
@@ -1342,7 +1339,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:10">
@@ -1365,7 +1362,7 @@
         <v>5</v>
       </c>
       <c r="I16" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:9">
@@ -1388,7 +1385,7 @@
         <v>5</v>
       </c>
       <c r="I17" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1487,7 +1484,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1513,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1539,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1565,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1591,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
